--- a/Output/PowerPoint_Figures/Fig_S4/Fig_S4a_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_S4/Fig_S4a_data.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,34 +418,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TPR_Lower</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>TPR_Upper</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
@@ -477,7 +465,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
@@ -497,7 +485,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
@@ -517,7 +505,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
@@ -537,7 +525,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
@@ -577,7 +565,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
@@ -597,7 +585,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
@@ -617,7 +605,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
@@ -637,7 +625,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
@@ -657,7 +645,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
@@ -697,7 +685,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
@@ -717,7 +705,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
@@ -737,7 +725,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
@@ -757,7 +745,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
@@ -777,7 +765,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
@@ -797,7 +785,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
@@ -817,7 +805,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
@@ -837,7 +825,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
@@ -857,7 +845,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="n">
@@ -877,7 +865,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
@@ -897,7 +885,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="n">
@@ -917,7 +905,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
@@ -937,7 +925,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +945,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
@@ -977,7 +965,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="n">
@@ -997,7 +985,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="n">
@@ -1017,7 +1005,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="n">
@@ -1037,7 +1025,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="n">
@@ -1057,7 +1045,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="n">
@@ -1077,7 +1065,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="n">
@@ -1097,7 +1085,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="n">
@@ -1117,7 +1105,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="n">
@@ -1157,7 +1145,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="n">
@@ -1177,7 +1165,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="n">
@@ -1197,7 +1185,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="n">
@@ -1217,7 +1205,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="n">
@@ -1237,7 +1225,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="n">
@@ -1257,7 +1245,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="n">
@@ -1277,7 +1265,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="n">
@@ -1297,7 +1285,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="n">
@@ -1317,7 +1305,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="n">
@@ -1337,7 +1325,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="n">
@@ -1357,7 +1345,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="n">
@@ -1377,7 +1365,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="n">
@@ -1397,7 +1385,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="n">
@@ -1417,7 +1405,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="n">
@@ -1437,7 +1425,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="n">
@@ -1457,7 +1445,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="n">
@@ -1477,7 +1465,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="n">
@@ -1497,7 +1485,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="n">
@@ -1517,7 +1505,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="n">
@@ -1537,7 +1525,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="n">
@@ -1557,7 +1545,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="n">
@@ -1577,7 +1565,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="n">
@@ -1597,7 +1585,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="n">
@@ -1617,7 +1605,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="n">
@@ -1637,7 +1625,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="n">
@@ -1657,7 +1645,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="n">
@@ -1677,7 +1665,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="n">
@@ -1697,7 +1685,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="n">
@@ -1717,7 +1705,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="n">
@@ -1737,7 +1725,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="n">
@@ -1757,7 +1745,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="n">
@@ -1777,7 +1765,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="n">
@@ -1797,7 +1785,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="n">
@@ -1817,7 +1805,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="n">
@@ -1837,7 +1825,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="n">
@@ -1857,7 +1845,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="n">
@@ -1877,7 +1865,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="n">
@@ -1897,7 +1885,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="n">
@@ -1917,7 +1905,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="n">
@@ -1937,7 +1925,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="n">
@@ -1957,7 +1945,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="n">
@@ -1977,7 +1965,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="n">
@@ -1997,7 +1985,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="n">
@@ -2017,7 +2005,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="n">
@@ -2037,7 +2025,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="n">
@@ -2057,7 +2045,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="n">
@@ -2077,7 +2065,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="n">
@@ -2097,7 +2085,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="n">
@@ -2117,7 +2105,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="n">
@@ -2137,7 +2125,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="n">
@@ -2157,7 +2145,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="n">
@@ -2177,7 +2165,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="n">
@@ -2197,7 +2185,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="n">
@@ -2217,7 +2205,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="n">
@@ -2237,7 +2225,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="n">
@@ -2257,7 +2245,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="n">
@@ -2277,7 +2265,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="n">
@@ -2297,7 +2285,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="n">
@@ -2317,7 +2305,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="n">
@@ -2337,7 +2325,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="n">
@@ -2357,7 +2345,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="n">
@@ -2377,7 +2365,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="n">
@@ -2397,7 +2385,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="n">
@@ -2417,7 +2405,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="n">
@@ -2437,7 +2425,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="n">
@@ -2471,34 +2459,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TPR_Lower</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>TPR_Upper</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
@@ -2518,7 +2506,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
@@ -2538,7 +2526,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
@@ -2558,7 +2546,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
@@ -2578,7 +2566,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
@@ -2598,7 +2586,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
@@ -2618,7 +2606,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
@@ -2638,7 +2626,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
@@ -2658,7 +2646,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
@@ -2678,7 +2666,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
@@ -2698,7 +2686,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
@@ -2718,7 +2706,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
@@ -2738,7 +2726,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
@@ -2758,7 +2746,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
@@ -2778,7 +2766,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
@@ -2798,7 +2786,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
@@ -2818,7 +2806,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
@@ -2838,7 +2826,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
@@ -2858,7 +2846,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
@@ -2878,7 +2866,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
@@ -2898,7 +2886,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="n">
@@ -2918,7 +2906,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
@@ -2938,7 +2926,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="n">
@@ -2958,7 +2946,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
@@ -2978,7 +2966,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
@@ -2998,7 +2986,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
@@ -3018,7 +3006,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="n">
@@ -3038,7 +3026,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="n">
@@ -3058,7 +3046,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="n">
@@ -3078,7 +3066,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="n">
@@ -3098,7 +3086,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="n">
@@ -3118,7 +3106,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="n">
@@ -3138,7 +3126,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="n">
@@ -3158,7 +3146,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="n">
@@ -3178,7 +3166,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="n">
@@ -3198,7 +3186,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="n">
@@ -3218,7 +3206,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="n">
@@ -3238,7 +3226,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="n">
@@ -3258,7 +3246,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="n">
@@ -3278,7 +3266,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="n">
@@ -3298,7 +3286,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="n">
@@ -3318,7 +3306,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="n">
@@ -3338,7 +3326,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="n">
@@ -3358,7 +3346,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="n">
@@ -3378,7 +3366,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="n">
@@ -3398,7 +3386,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="n">
@@ -3418,7 +3406,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="n">
@@ -3438,7 +3426,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="n">
@@ -3458,7 +3446,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="n">
@@ -3478,7 +3466,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="n">
@@ -3498,7 +3486,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="n">
@@ -3518,7 +3506,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="n">
@@ -3538,7 +3526,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="n">
@@ -3558,7 +3546,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="n">
@@ -3578,7 +3566,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="n">
@@ -3598,7 +3586,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="n">
@@ -3618,7 +3606,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="n">
@@ -3638,7 +3626,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="n">
@@ -3658,7 +3646,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="n">
@@ -3678,7 +3666,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="n">
@@ -3698,7 +3686,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="n">
@@ -3718,7 +3706,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="n">
@@ -3738,7 +3726,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="n">
@@ -3758,7 +3746,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="n">
@@ -3778,7 +3766,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="n">
@@ -3798,7 +3786,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="n">
@@ -3818,7 +3806,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="n">
@@ -3838,7 +3826,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="n">
@@ -3858,7 +3846,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="n">
@@ -3878,7 +3866,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="n">
@@ -3898,7 +3886,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="n">
@@ -3918,7 +3906,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="n">
@@ -3938,7 +3926,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="n">
@@ -3958,7 +3946,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="n">
@@ -3978,7 +3966,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="n">
@@ -3998,7 +3986,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="n">
@@ -4018,7 +4006,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="n">
@@ -4038,7 +4026,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="n">
@@ -4058,7 +4046,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="n">
@@ -4078,7 +4066,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="n">
@@ -4098,7 +4086,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="n">
@@ -4118,7 +4106,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="n">
@@ -4138,7 +4126,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="n">
@@ -4158,7 +4146,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="n">
@@ -4178,7 +4166,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="n">
@@ -4198,7 +4186,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="n">
@@ -4218,7 +4206,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="n">
@@ -4238,7 +4226,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="n">
@@ -4258,7 +4246,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="n">
@@ -4278,7 +4266,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="n">
@@ -4298,7 +4286,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="n">
@@ -4318,7 +4306,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="n">
@@ -4338,7 +4326,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="n">
@@ -4358,7 +4346,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="n">
@@ -4378,7 +4366,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="n">
@@ -4398,7 +4386,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="n">
@@ -4418,7 +4406,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="n">
@@ -4438,7 +4426,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="n">
@@ -4458,7 +4446,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="n">
@@ -4478,7 +4466,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="n">
